--- a/data-manipulation-scripts/sheets-cleanup/sheets/COXIM - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/COXIM - 24_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -23,24 +23,6 @@
   </si>
   <si>
     <t>PREÇO</t>
-  </si>
-  <si>
-    <t>7898676081439</t>
-  </si>
-  <si>
-    <t>JOGO BUCHA COROA CONTROLSEALS CG TITAN KS</t>
-  </si>
-  <si>
-    <t>7898751863394</t>
-  </si>
-  <si>
-    <t>JOGO BUCHA COROA EXTREMO CG TITAN</t>
-  </si>
-  <si>
-    <t>7893986133816</t>
-  </si>
-  <si>
-    <t>JOGO BUCHA COROA PECA+ BIZ100</t>
   </si>
   <si>
     <t>7899248138926</t>
@@ -119,18 +101,6 @@
   </si>
   <si>
     <t>COXIM COROA YAMAHA</t>
-  </si>
-  <si>
-    <t>7893986507006</t>
-  </si>
-  <si>
-    <t>COXIM AMORTECEDOR TWISTER/ CB300/ XRE300/ TORNADO/ XR/ XLR</t>
-  </si>
-  <si>
-    <t>5637300001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COXIM APOIO TANQUE  WR XTREME CG150 </t>
   </si>
 </sst>
 </file>
@@ -434,231 +404,213 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
         <v>6.0</v>
       </c>
-      <c r="D2" s="2">
-        <v>12.0</v>
+      <c r="D4" s="2">
+        <v>15.0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2">
         <v>1.0</v>
       </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2">
         <v>2.0</v>
       </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
+      <c r="A9" s="2">
+        <v>7.899468089374E12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
-      <c r="D9" s="2">
-        <v>15.0</v>
-      </c>
+      <c r="D9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
-      <c r="D10" s="2">
-        <v>20.0</v>
-      </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>28.0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1"/>
+      <c r="A12" s="2">
+        <v>6.974288490409E12</v>
+      </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="2">
-        <v>7.899468089374E12</v>
+      <c r="A14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="D15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="D16" s="2">
-        <v>28.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>6.974288490409E12</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="D19" s="2">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="D21" s="2">
         <v>50.0</v>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="4"/>
@@ -679,12 +631,8 @@
       <c r="D24" s="3"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="A25" s="4"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
@@ -701,12 +649,8 @@
       <c r="D27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
@@ -6542,56 +6486,14 @@
       <c r="C1000" s="3"/>
       <c r="D1000" s="3"/>
     </row>
-    <row r="1001">
-      <c r="A1001" s="4"/>
-      <c r="B1001" s="3"/>
-      <c r="C1001" s="3"/>
-      <c r="D1001" s="3"/>
-    </row>
-    <row r="1002">
-      <c r="A1002" s="4"/>
-      <c r="B1002" s="3"/>
-      <c r="C1002" s="3"/>
-      <c r="D1002" s="3"/>
-    </row>
-    <row r="1003">
-      <c r="A1003" s="4"/>
-      <c r="B1003" s="3"/>
-      <c r="C1003" s="3"/>
-      <c r="D1003" s="3"/>
-    </row>
-    <row r="1004">
-      <c r="A1004" s="4"/>
-      <c r="B1004" s="3"/>
-      <c r="C1004" s="3"/>
-      <c r="D1004" s="3"/>
-    </row>
-    <row r="1005">
-      <c r="A1005" s="4"/>
-      <c r="B1005" s="3"/>
-      <c r="C1005" s="3"/>
-      <c r="D1005" s="3"/>
-    </row>
-    <row r="1006">
-      <c r="A1006" s="4"/>
-      <c r="B1006" s="3"/>
-      <c r="C1006" s="3"/>
-      <c r="D1006" s="3"/>
-    </row>
-    <row r="1007">
-      <c r="A1007" s="4"/>
-      <c r="B1007" s="3"/>
-      <c r="C1007" s="3"/>
-      <c r="D1007" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1007">
+  <conditionalFormatting sqref="A1:A1000">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A13 A15:A16 A18:A1007">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A8 A10:A11 A13:A1000">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
